--- a/requirements-extractor/samples/sample_output.xlsx
+++ b/requirements-extractor/samples/sample_output.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Requirements'!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Requirements'!$A$1:$N$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +60,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -73,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -82,6 +87,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -450,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -463,9 +471,10 @@
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -521,15 +530,20 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Polarity</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Keywords</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -544,23 +558,35 @@
           <t>sample_spec.docx</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>3. System Requirements &gt; 3.1 Authentication</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>3.1 Authentication</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Preamble</t>
+          <t>Table 1, Row 2</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Paragraph</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Paragraph 1</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Auth Service</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>This specification captures requirements for the Example System.</t>
+          <t>The Auth Service shall authenticate every user before granting access to protected resources.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -570,15 +596,20 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>requirements</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>shall</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -591,12 +622,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>3. System Requirements</t>
+          <t>3. System Requirements &gt; 3.1 Authentication</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Auth Service</t>
+          <t>3.1 Authentication</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -606,7 +637,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Paragraph 1</t>
+          <t>Paragraph 2</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -617,7 +648,7 @@
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>The Auth Service shall authenticate every user before granting access to protected resources.</t>
+          <t>Failed login attempts must be rate-limited to five per minute per account.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -627,72 +658,86 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>shall</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
+          <t>must</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>sample_spec.docx</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3. System Requirements</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>3. System Requirements &gt; 3.1 Authentication</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>3.1 Authentication</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Table 1, Row 2</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Paragraph 3</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Auth Service</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Table 1, Row 2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Paragraph 2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Auth Service</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Failed login attempts must be rate-limited to five per minute per account.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Passwords should be hashed with bcrypt.</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>should</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Soft language — verify with author whether this is a binding requirement.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -705,12 +750,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>3. System Requirements</t>
+          <t>3. System Requirements &gt; 3.1 Authentication</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Auth Service</t>
+          <t>3.1 Authentication</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -720,7 +765,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Paragraph 3</t>
+          <t>Bullet 1</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -731,7 +776,7 @@
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Passwords should be hashed with bcrypt.</t>
+          <t>Sessions will expire after 30 minutes of inactivity.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -741,76 +786,90 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>should</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
+          <t>will</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Soft language — verify with author whether this is a binding requirement.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>sample_spec.docx</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3. System Requirements</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>3. System Requirements &gt; 3.1 Authentication</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>3.1 Authentication</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Table 1, Row 2</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Bullet 2</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Auth Service</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Table 1, Row 2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Bullet 1</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Auth Service</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Sessions will expire after 30 minutes of inactivity.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>will</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>The Auth Service may cache public keys for up to one hour.</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>may</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Soft language — verify with author whether this is a binding requirement.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -823,33 +882,37 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>3. System Requirements</t>
+          <t>3. System Requirements &gt; 3.1 Authentication</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
+          <t>3.1 Authentication</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Table 1, Row 2</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Bullet 3</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
           <t>Auth Service</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Table 1, Row 2</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Bullet 2</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Auth Service</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Ground Control</t>
+        </is>
+      </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>The Auth Service may cache public keys for up to one hour.</t>
+          <t>Ground Control can override a lockout for operational emergencies.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -859,84 +922,90 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>may</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
+          <t>can</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Soft language — verify with author whether this is a binding requirement.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>sample_spec.docx</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>3. System Requirements</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Auth Service</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Table 1, Row 2</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Bullet 3</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Auth Service</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3. System Requirements &gt; 3.2 Telemetry</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3.2 Telemetry</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Table 1, Row 4</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Paragraph 1</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Flight Software</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Ground Control</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Ground Control can override a lockout for operational emergencies.</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>can</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>Soft language — verify with author whether this is a binding requirement.</t>
-        </is>
-      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>The Flight Software shall transmit telemetry packets to Ground Control at 1 Hz during nominal operations.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>shall</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -949,291 +1018,312 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3. System Requirements</t>
+          <t>3. System Requirements &gt; 3.2 Telemetry</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>3.2 Telemetry</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Table 1, Row 4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Paragraph 2</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>Flight Software</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Telemetry packets must include a timestamp, health bits, and a CRC-32 checksum.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>must</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>sample_spec.docx</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>3. System Requirements &gt; 3.2 Telemetry</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>3.2 Telemetry</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Table 1, Row 4</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Paragraph 3</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Flight Software</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>During safe mode, FSW should reduce telemetry rate to 0.1 Hz to conserve bandwidth.</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>should</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Soft language — verify with author whether this is a binding requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>sample_spec.docx</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3. System Requirements &gt; 3.2 Telemetry</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3.2 Telemetry</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Table 1, Row 5</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Paragraph 1</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Flight Software</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Ground Control</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>The Flight Software shall transmit telemetry packets to Ground Control at 1 Hz during nominal operations.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Ground Control shall acknowledge every telemetry burst within 3 seconds.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>shall</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>sample_spec.docx</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3. System Requirements</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Flight Software</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Table 1, Row 4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>3. System Requirements &gt; 3.2 Telemetry</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>3.2 Telemetry</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Table 1, Row 5</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Paragraph 2</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Flight Software</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Telemetry packets must include a timestamp, health bits, and a CRC-32 checksum.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Ground Control</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Mission Control may request on-demand housekeeping packets during pass windows.</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>may</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Soft language — verify with author whether this is a binding requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>sample_spec.docx</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3. System Requirements &gt; 3.3 Payload Operations</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3.3 Payload Operations</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Table 1, Row 7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Paragraph 1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Payload Operator</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>The Payload Operator shall schedule imaging tasks at least 24 hours in advance.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>shall</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>sample_spec.docx</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>3. System Requirements</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Flight Software</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Table 1, Row 4</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Paragraph 3</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Flight Software</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>During safe mode, FSW should reduce telemetry rate to 0.1 Hz to conserve bandwidth.</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>should</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>Soft language — verify with author whether this is a binding requirement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>sample_spec.docx</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3. System Requirements</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Ground Control</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Table 1, Row 5</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Paragraph 1</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Ground Control</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Ground Control shall acknowledge every telemetry burst within 3 seconds.</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>shall</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>sample_spec.docx</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>3. System Requirements</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Ground Control</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Table 1, Row 5</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Paragraph 2</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Ground Control</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Mission Control may request on-demand housekeeping packets during pass windows.</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>may</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>Soft language — verify with author whether this is a binding requirement.</t>
-        </is>
-      </c>
+      <c r="N13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1246,233 +1336,195 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3. System Requirements</t>
+          <t>3. System Requirements &gt; 3.3 Payload Operations</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>3.3 Payload Operations</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Table 1, Row 7</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Bullet 1</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>Payload Operator</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Ground Control</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Emergency tasking requests must be routed through Ground Control.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>must</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>sample_spec.docx</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>3. System Requirements &gt; 3.3 Payload Operations</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>3.3 Payload Operations</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Table 1, Row 7</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Paragraph 1</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Bullet 2</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Payload Operator</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>The Payload Operator shall schedule imaging tasks at least 24 hours in advance.</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>shall</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>PL Op should verify target coordinates before uploading a task.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Soft</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>should</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Soft language — verify with author whether this is a binding requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>sample_spec.docx</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>3. System Requirements</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>3. System Requirements &gt; 3.3 Payload Operations</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>3.3 Payload Operations</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Table 1, Row 7</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Paragraph 2</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Payload Operator</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Table 1, Row 7</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Bullet 1</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Payload Operator</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Ground Control</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Emergency tasking requests must be routed through Ground Control.</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>sample_spec.docx</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>3. System Requirements</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Payload Operator</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Table 1, Row 7</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Bullet 2</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Payload Operator</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>PL Op should verify target coordinates before uploading a task.</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Note: this paragraph contains no requirement keywords and should not appear in the output.</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>Soft</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>should</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>Soft language — verify with author whether this is a binding requirement.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>sample_spec.docx</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>3. System Requirements</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Payload Operator</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Table 1, Row 7</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Paragraph 2</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Payload Operator</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Note: this paragraph contains no requirement keywords and should not appear in the output.</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>requirement, should</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M17"/>
+  <autoFilter ref="A1:N16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1483,7 +1535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1491,41 +1543,41 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Total requirements</t>
         </is>
       </c>
       <c r="B1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Hard requirements</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Soft (needs review)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr"/>
+      <c r="A4" s="5" t="inlineStr"/>
       <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Top actors</t>
         </is>
@@ -1533,7 +1585,7 @@
       <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Auth Service</t>
         </is>
@@ -1543,7 +1595,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Payload Operator</t>
         </is>
@@ -1553,7 +1605,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Flight Software</t>
         </is>
@@ -1563,23 +1615,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Ground Control</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>(no primary actor)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
